--- a/Assets/__project/4_excel/StatusConsTable.xlsx
+++ b/Assets/__project/4_excel/StatusConsTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\CrispyDice\Assets\__project\4_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B3CFF1-0847-436A-BAEA-CEF6ADC73921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF7D757-755C-4A99-80AD-170302B4D043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9045" yWindow="3750" windowWidth="21600" windowHeight="11295" xr2:uid="{43D3D548-8632-477F-992E-E4FF216C7F3F}"/>
+    <workbookView xWindow="30495" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{43D3D548-8632-477F-992E-E4FF216C7F3F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -467,10 +467,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="1">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -478,10 +478,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C4" s="1">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
